--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_araucania.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>1099744</v>
+      </c>
+      <c r="C2">
+        <v>1032164</v>
+      </c>
+      <c r="D2">
         <v>106.5474091326572</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Malleco</t>
         </is>
       </c>
       <c r="C2">
-        <v>187514</v>
+        <v>233318</v>
       </c>
       <c r="D2">
-        <v>196063</v>
+        <v>216365</v>
       </c>
       <c r="E2">
-        <v>95.63966684178044</v>
+        <v>107.8353707854782</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,96 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Cautín</t>
         </is>
       </c>
       <c r="C3">
-        <v>222542</v>
+        <v>866426</v>
       </c>
       <c r="D3">
-        <v>202178</v>
+        <v>815799</v>
       </c>
       <c r="E3">
-        <v>110.0723125166932</v>
+        <v>106.2058178546431</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>44903</v>
+      </c>
+      <c r="D2">
+        <v>58997</v>
+      </c>
+      <c r="E2">
+        <v>76.11064969405223</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>67281</v>
+      </c>
+      <c r="D3">
+        <v>66254</v>
+      </c>
+      <c r="E3">
+        <v>101.5500950885984</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +650,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>10-14</t>
         </is>
       </c>
       <c r="C4">
-        <v>239528</v>
+        <v>75330</v>
       </c>
       <c r="D4">
-        <v>215540</v>
+        <v>70812</v>
       </c>
       <c r="E4">
-        <v>111.1292567504871</v>
+        <v>106.3802745297407</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +671,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>15-19</t>
         </is>
       </c>
       <c r="C5">
-        <v>276073</v>
+        <v>74407</v>
       </c>
       <c r="D5">
-        <v>258176</v>
+        <v>67213</v>
       </c>
       <c r="E5">
-        <v>106.9320928358949</v>
+        <v>110.7032865665868</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +692,269 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>20-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>174087</v>
+        <v>71241</v>
       </c>
       <c r="D6">
-        <v>160207</v>
+        <v>64322</v>
       </c>
       <c r="E6">
-        <v>108.663791220109</v>
+        <v>110.7568172631448</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>76894</v>
+      </c>
+      <c r="D7">
+        <v>70643</v>
+      </c>
+      <c r="E7">
+        <v>108.8487182027943</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>86247</v>
+      </c>
+      <c r="D8">
+        <v>76040</v>
+      </c>
+      <c r="E8">
+        <v>113.4231983166754</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>79547</v>
+      </c>
+      <c r="D9">
+        <v>70028</v>
+      </c>
+      <c r="E9">
+        <v>113.5931341749015</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>73734</v>
+      </c>
+      <c r="D10">
+        <v>69472</v>
+      </c>
+      <c r="E10">
+        <v>106.1348456932289</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>67276</v>
+      </c>
+      <c r="D11">
+        <v>68548</v>
+      </c>
+      <c r="E11">
+        <v>98.14436599171384</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>72681</v>
+      </c>
+      <c r="D12">
+        <v>65720</v>
+      </c>
+      <c r="E12">
+        <v>110.5919050517346</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>70392</v>
+      </c>
+      <c r="D13">
+        <v>65559</v>
+      </c>
+      <c r="E13">
+        <v>107.3719855397428</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>65724</v>
+      </c>
+      <c r="D14">
+        <v>58349</v>
+      </c>
+      <c r="E14">
+        <v>112.6394625443452</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>54977</v>
+      </c>
+      <c r="D15">
+        <v>50787</v>
+      </c>
+      <c r="E15">
+        <v>108.2501427530667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>42752</v>
+      </c>
+      <c r="D16">
+        <v>40239</v>
+      </c>
+      <c r="E16">
+        <v>106.2451850195084</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>32064</v>
+      </c>
+      <c r="D17">
+        <v>28909</v>
+      </c>
+      <c r="E17">
+        <v>110.9135563319382</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>44294</v>
+      </c>
+      <c r="D18">
+        <v>40272</v>
+      </c>
+      <c r="E18">
+        <v>109.98708780294</v>
       </c>
     </row>
   </sheetData>
